--- a/数据表/Datas/GlobalConfig_全局配置.xlsx
+++ b/数据表/Datas/GlobalConfig_全局配置.xlsx
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="111" uniqueCount="84">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="115" uniqueCount="86">
   <si>
     <t>##var#column</t>
   </si>
@@ -53,7 +53,7 @@
       <rPr>
         <sz val="12"/>
         <color rgb="FF375623"/>
-        <rFont val="宋体"/>
+        <rFont val="微软雅黑"/>
         <charset val="134"/>
       </rPr>
       <t>单局与撤离</t>
@@ -79,7 +79,7 @@
       <rPr>
         <sz val="12"/>
         <color rgb="FF202020"/>
-        <rFont val="宋体"/>
+        <rFont val="微软雅黑"/>
         <charset val="134"/>
       </rPr>
       <t>单局时间上限，毫秒</t>
@@ -93,7 +93,7 @@
       <rPr>
         <sz val="12"/>
         <color rgb="FF202020"/>
-        <rFont val="宋体"/>
+        <rFont val="微软雅黑"/>
         <charset val="134"/>
       </rPr>
       <t>小地图标记撤离点的时间，毫秒</t>
@@ -110,7 +110,7 @@
       <rPr>
         <sz val="12"/>
         <color rgb="FF202020"/>
-        <rFont val="宋体"/>
+        <rFont val="微软雅黑"/>
         <charset val="134"/>
       </rPr>
       <t>地图定义</t>
@@ -128,7 +128,7 @@
       <rPr>
         <sz val="12"/>
         <color rgb="FF202020"/>
-        <rFont val="宋体"/>
+        <rFont val="微软雅黑"/>
         <charset val="134"/>
       </rPr>
       <t>路径（相对于</t>
@@ -146,7 +146,7 @@
       <rPr>
         <sz val="12"/>
         <color rgb="FF202020"/>
-        <rFont val="宋体"/>
+        <rFont val="微软雅黑"/>
         <charset val="134"/>
       </rPr>
       <t>）</t>
@@ -163,7 +163,7 @@
       <rPr>
         <sz val="12"/>
         <color rgb="FF202020"/>
-        <rFont val="宋体"/>
+        <rFont val="微软雅黑"/>
         <charset val="134"/>
       </rPr>
       <t>逃跑返回地图后的保护时间，毫秒</t>
@@ -180,7 +180,7 @@
       <rPr>
         <sz val="12"/>
         <color rgb="FF202020"/>
-        <rFont val="宋体"/>
+        <rFont val="微软雅黑"/>
         <charset val="134"/>
       </rPr>
       <t>低威胁敌人小队实体</t>
@@ -197,7 +197,7 @@
       <rPr>
         <sz val="12"/>
         <color rgb="FF202020"/>
-        <rFont val="宋体"/>
+        <rFont val="微软雅黑"/>
         <charset val="134"/>
       </rPr>
       <t>中威胁敌人小队实体</t>
@@ -214,7 +214,7 @@
       <rPr>
         <sz val="12"/>
         <color rgb="FF202020"/>
-        <rFont val="宋体"/>
+        <rFont val="微软雅黑"/>
         <charset val="134"/>
       </rPr>
       <t>高威胁敌人小队实体</t>
@@ -230,7 +230,7 @@
     <r>
       <rPr>
         <sz val="12"/>
-        <rFont val="宋体"/>
+        <rFont val="微软雅黑"/>
         <charset val="134"/>
       </rPr>
       <t>撤离点实体</t>
@@ -247,7 +247,7 @@
       <rPr>
         <sz val="12"/>
         <color rgb="FF202020"/>
-        <rFont val="宋体"/>
+        <rFont val="微软雅黑"/>
         <charset val="134"/>
       </rPr>
       <t>玩家队伍领队实体</t>
@@ -264,7 +264,7 @@
       <rPr>
         <sz val="12"/>
         <color rgb="FF202020"/>
-        <rFont val="宋体"/>
+        <rFont val="微软雅黑"/>
         <charset val="134"/>
       </rPr>
       <t>玩家队伍其他实体</t>
@@ -274,6 +274,20 @@
     <t>CharacterRetinue</t>
   </si>
   <si>
+    <t>ItemEntity</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF202020"/>
+        <rFont val="微软雅黑"/>
+        <charset val="134"/>
+      </rPr>
+      <t>局内道具实体</t>
+    </r>
+  </si>
+  <si>
     <r>
       <t xml:space="preserve">##======== </t>
     </r>
@@ -281,7 +295,7 @@
       <rPr>
         <sz val="12"/>
         <color rgb="FF375623"/>
-        <rFont val="宋体"/>
+        <rFont val="微软雅黑"/>
         <charset val="134"/>
       </rPr>
       <t>敌人警惕与追击</t>
@@ -304,7 +318,7 @@
       <rPr>
         <sz val="12"/>
         <color rgb="FF202020"/>
-        <rFont val="宋体"/>
+        <rFont val="微软雅黑"/>
         <charset val="134"/>
       </rPr>
       <t>敌人丢失目标后返回巡逻的时间，毫秒</t>
@@ -318,7 +332,7 @@
       <rPr>
         <sz val="12"/>
         <color rgb="FF202020"/>
-        <rFont val="宋体"/>
+        <rFont val="微软雅黑"/>
         <charset val="134"/>
       </rPr>
       <t>敌人正面视野角度</t>
@@ -332,7 +346,7 @@
       <rPr>
         <sz val="12"/>
         <color rgb="FF202020"/>
-        <rFont val="宋体"/>
+        <rFont val="微软雅黑"/>
         <charset val="134"/>
       </rPr>
       <t>警惕值满值</t>
@@ -346,7 +360,7 @@
       <rPr>
         <sz val="12"/>
         <color rgb="FF375623"/>
-        <rFont val="宋体"/>
+        <rFont val="微软雅黑"/>
         <charset val="134"/>
       </rPr>
       <t>队伍与库存</t>
@@ -369,7 +383,7 @@
       <rPr>
         <sz val="12"/>
         <color rgb="FF202020"/>
-        <rFont val="宋体"/>
+        <rFont val="微软雅黑"/>
         <charset val="134"/>
       </rPr>
       <t>仓库格子数</t>
@@ -383,7 +397,7 @@
       <rPr>
         <sz val="12"/>
         <color rgb="FF202020"/>
-        <rFont val="宋体"/>
+        <rFont val="微软雅黑"/>
         <charset val="134"/>
       </rPr>
       <t>共享背包格子数</t>
@@ -397,7 +411,7 @@
       <rPr>
         <sz val="12"/>
         <color rgb="FF202020"/>
-        <rFont val="宋体"/>
+        <rFont val="微软雅黑"/>
         <charset val="134"/>
       </rPr>
       <t>保险箱格子数</t>
@@ -411,7 +425,7 @@
       <rPr>
         <sz val="12"/>
         <color rgb="FF202020"/>
-        <rFont val="宋体"/>
+        <rFont val="微软雅黑"/>
         <charset val="134"/>
       </rPr>
       <t>最少出战人数</t>
@@ -425,7 +439,7 @@
       <rPr>
         <sz val="12"/>
         <color rgb="FF202020"/>
-        <rFont val="宋体"/>
+        <rFont val="微软雅黑"/>
         <charset val="134"/>
       </rPr>
       <t>最多出战人数</t>
@@ -439,7 +453,7 @@
       <rPr>
         <sz val="12"/>
         <color rgb="FF202020"/>
-        <rFont val="宋体"/>
+        <rFont val="微软雅黑"/>
         <charset val="134"/>
       </rPr>
       <t>敌人队伍人数上限</t>
@@ -453,7 +467,7 @@
       <rPr>
         <sz val="12"/>
         <color rgb="FF375623"/>
-        <rFont val="宋体"/>
+        <rFont val="微软雅黑"/>
         <charset val="134"/>
       </rPr>
       <t>战斗与计时</t>
@@ -476,7 +490,7 @@
       <rPr>
         <sz val="12"/>
         <color rgb="FF202020"/>
-        <rFont val="宋体"/>
+        <rFont val="微软雅黑"/>
         <charset val="134"/>
       </rPr>
       <t>非全员阵亡结算时阵亡角色恢复</t>
@@ -499,7 +513,7 @@
       <rPr>
         <sz val="12"/>
         <color rgb="FF202020"/>
-        <rFont val="宋体"/>
+        <rFont val="微软雅黑"/>
         <charset val="134"/>
       </rPr>
       <t>非全员阵亡结算时阵亡角色恢复</t>
@@ -522,7 +536,7 @@
       <rPr>
         <sz val="12"/>
         <color rgb="FF202020"/>
-        <rFont val="宋体"/>
+        <rFont val="微软雅黑"/>
         <charset val="134"/>
       </rPr>
       <t>逃跑成功率，千分比原型初值</t>
@@ -539,7 +553,7 @@
       <rPr>
         <sz val="12"/>
         <color rgb="FF202020"/>
-        <rFont val="宋体"/>
+        <rFont val="微软雅黑"/>
         <charset val="134"/>
       </rPr>
       <t>首版墙体是否阻挡警惕视野</t>
@@ -553,7 +567,7 @@
       <rPr>
         <sz val="12"/>
         <color rgb="FF202020"/>
-        <rFont val="宋体"/>
+        <rFont val="微软雅黑"/>
         <charset val="134"/>
       </rPr>
       <t>战斗中是否暂停单局计时</t>
@@ -567,7 +581,7 @@
       <rPr>
         <sz val="12"/>
         <color rgb="FF202020"/>
-        <rFont val="宋体"/>
+        <rFont val="微软雅黑"/>
         <charset val="134"/>
       </rPr>
       <t>打开背包是否暂停单局计时</t>
@@ -581,7 +595,7 @@
       <rPr>
         <sz val="12"/>
         <color rgb="FF202020"/>
-        <rFont val="宋体"/>
+        <rFont val="微软雅黑"/>
         <charset val="134"/>
       </rPr>
       <t>暂停菜单是否暂停单局计时</t>
@@ -595,7 +609,7 @@
       <rPr>
         <sz val="12"/>
         <color rgb="FF202020"/>
-        <rFont val="宋体"/>
+        <rFont val="微软雅黑"/>
         <charset val="134"/>
       </rPr>
       <t>敌人自动行动间隔</t>
@@ -612,7 +626,7 @@
       <rPr>
         <sz val="12"/>
         <color rgb="FF202020"/>
-        <rFont val="宋体"/>
+        <rFont val="微软雅黑"/>
         <charset val="134"/>
       </rPr>
       <t>时间注册超时帧数</t>
@@ -626,7 +640,7 @@
       <rPr>
         <sz val="12"/>
         <color rgb="FF202020"/>
-        <rFont val="宋体"/>
+        <rFont val="微软雅黑"/>
         <charset val="134"/>
       </rPr>
       <t>卡片状态文本动画时间</t>
@@ -640,7 +654,7 @@
       <rPr>
         <sz val="12"/>
         <color rgb="FF202020"/>
-        <rFont val="宋体"/>
+        <rFont val="微软雅黑"/>
         <charset val="134"/>
       </rPr>
       <t>卡片状态文本浮动高度</t>
@@ -654,7 +668,7 @@
       <rPr>
         <sz val="12"/>
         <color rgb="FF375623"/>
-        <rFont val="宋体"/>
+        <rFont val="微软雅黑"/>
         <charset val="134"/>
       </rPr>
       <t>新存档</t>
@@ -680,7 +694,7 @@
       <rPr>
         <sz val="12"/>
         <color rgb="FF202020"/>
-        <rFont val="宋体"/>
+        <rFont val="微软雅黑"/>
         <charset val="134"/>
       </rPr>
       <t>新存档直接拥有的角色</t>
@@ -883,18 +897,18 @@
     <font>
       <sz val="12"/>
       <color rgb="FF202020"/>
-      <name val="宋体"/>
+      <name val="微软雅黑"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="12"/>
-      <name val="宋体"/>
+      <name val="微软雅黑"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="12"/>
       <color rgb="FF375623"/>
-      <name val="宋体"/>
+      <name val="微软雅黑"/>
       <charset val="134"/>
     </font>
   </fonts>
@@ -1385,7 +1399,7 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="49"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="49" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="49" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1410,9 +1424,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -2085,11 +2096,19 @@
       <c r="F12" s="7"/>
     </row>
     <row r="13" customHeight="1" spans="1:6">
-      <c r="A13" s="7"/>
+      <c r="A13" s="7" t="s">
+        <v>35</v>
+      </c>
       <c r="B13" s="7"/>
-      <c r="C13" s="7"/>
-      <c r="D13" s="7"/>
-      <c r="E13" s="10"/>
+      <c r="C13" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="D13" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="E13" s="8" t="s">
+        <v>35</v>
+      </c>
       <c r="F13" s="7"/>
     </row>
     <row r="14" customHeight="1" spans="1:6">
@@ -2102,7 +2121,7 @@
     </row>
     <row r="15" customHeight="1" spans="1:6">
       <c r="A15" s="5" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="B15" s="5"/>
       <c r="C15" s="5"/>
@@ -2112,14 +2131,14 @@
     </row>
     <row r="16" customHeight="1" spans="1:6">
       <c r="A16" s="7" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="B16" s="7"/>
       <c r="C16" s="7" t="s">
         <v>6</v>
       </c>
       <c r="D16" s="7" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="E16" s="8">
         <v>3000</v>
@@ -2128,14 +2147,14 @@
     </row>
     <row r="17" customHeight="1" spans="1:6">
       <c r="A17" s="7" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="B17" s="7"/>
       <c r="C17" s="7" t="s">
         <v>6</v>
       </c>
       <c r="D17" s="7" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="E17" s="8">
         <v>180</v>
@@ -2144,14 +2163,14 @@
     </row>
     <row r="18" customHeight="1" spans="1:6">
       <c r="A18" s="7" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="B18" s="7"/>
       <c r="C18" s="7" t="s">
         <v>6</v>
       </c>
       <c r="D18" s="7" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="E18" s="8">
         <v>1000</v>
@@ -2168,7 +2187,7 @@
     </row>
     <row r="20" customHeight="1" spans="1:6">
       <c r="A20" s="5" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="B20" s="5"/>
       <c r="C20" s="5"/>
@@ -2178,14 +2197,14 @@
     </row>
     <row r="21" customHeight="1" spans="1:6">
       <c r="A21" s="7" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="B21" s="7"/>
       <c r="C21" s="7" t="s">
         <v>6</v>
       </c>
       <c r="D21" s="7" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="E21" s="8">
         <v>120</v>
@@ -2194,14 +2213,14 @@
     </row>
     <row r="22" customHeight="1" spans="1:6">
       <c r="A22" s="7" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="B22" s="7"/>
       <c r="C22" s="7" t="s">
         <v>6</v>
       </c>
       <c r="D22" s="7" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="E22" s="8">
         <v>30</v>
@@ -2210,14 +2229,14 @@
     </row>
     <row r="23" customHeight="1" spans="1:6">
       <c r="A23" s="7" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="B23" s="7"/>
       <c r="C23" s="7" t="s">
         <v>6</v>
       </c>
       <c r="D23" s="7" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="E23" s="8">
         <v>5</v>
@@ -2226,14 +2245,14 @@
     </row>
     <row r="24" customHeight="1" spans="1:6">
       <c r="A24" s="7" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="B24" s="7"/>
       <c r="C24" s="7" t="s">
         <v>6</v>
       </c>
       <c r="D24" s="7" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="E24" s="8">
         <v>1</v>
@@ -2242,14 +2261,14 @@
     </row>
     <row r="25" customHeight="1" spans="1:6">
       <c r="A25" s="7" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="B25" s="7"/>
       <c r="C25" s="7" t="s">
         <v>6</v>
       </c>
       <c r="D25" s="7" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="E25" s="8">
         <v>4</v>
@@ -2258,14 +2277,14 @@
     </row>
     <row r="26" customHeight="1" spans="1:6">
       <c r="A26" s="7" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="B26" s="7"/>
       <c r="C26" s="7" t="s">
         <v>6</v>
       </c>
       <c r="D26" s="7" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="E26" s="8">
         <v>4</v>
@@ -2282,7 +2301,7 @@
     </row>
     <row r="28" customHeight="1" spans="1:6">
       <c r="A28" s="5" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="B28" s="5"/>
       <c r="C28" s="5"/>
@@ -2292,14 +2311,14 @@
     </row>
     <row r="29" customHeight="1" spans="1:6">
       <c r="A29" s="7" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="B29" s="7"/>
       <c r="C29" s="7" t="s">
         <v>6</v>
       </c>
       <c r="D29" s="7" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="E29" s="8">
         <v>1</v>
@@ -2308,14 +2327,14 @@
     </row>
     <row r="30" customHeight="1" spans="1:6">
       <c r="A30" s="7" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="B30" s="7"/>
       <c r="C30" s="7" t="s">
         <v>6</v>
       </c>
       <c r="D30" s="7" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="E30" s="8">
         <v>1</v>
@@ -2324,14 +2343,14 @@
     </row>
     <row r="31" customHeight="1" spans="1:6">
       <c r="A31" s="7" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="B31" s="7"/>
       <c r="C31" s="7" t="s">
         <v>6</v>
       </c>
       <c r="D31" s="7" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="E31" s="8">
         <v>500</v>
@@ -2340,14 +2359,14 @@
     </row>
     <row r="32" customHeight="1" spans="1:6">
       <c r="A32" s="7" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="B32" s="7"/>
       <c r="C32" s="7" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="D32" s="7" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="E32" s="8" t="b">
         <v>0</v>
@@ -2356,14 +2375,14 @@
     </row>
     <row r="33" customHeight="1" spans="1:6">
       <c r="A33" s="7" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="B33" s="7"/>
       <c r="C33" s="7" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="D33" s="7" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="E33" s="8" t="b">
         <v>1</v>
@@ -2372,14 +2391,14 @@
     </row>
     <row r="34" customHeight="1" spans="1:6">
       <c r="A34" s="7" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="B34" s="7"/>
       <c r="C34" s="7" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="D34" s="7" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="E34" s="8" t="b">
         <v>0</v>
@@ -2388,14 +2407,14 @@
     </row>
     <row r="35" customHeight="1" spans="1:6">
       <c r="A35" s="7" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="B35" s="7"/>
       <c r="C35" s="7" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="D35" s="7" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="E35" s="8" t="b">
         <v>1</v>
@@ -2404,14 +2423,14 @@
     </row>
     <row r="36" customHeight="1" spans="1:6">
       <c r="A36" s="7" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="B36" s="7"/>
       <c r="C36" s="7" t="s">
         <v>6</v>
       </c>
       <c r="D36" s="7" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="E36" s="8">
         <v>600</v>
@@ -2420,14 +2439,14 @@
     </row>
     <row r="37" customHeight="1" spans="1:6">
       <c r="A37" s="7" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="B37" s="7"/>
       <c r="C37" s="7" t="s">
         <v>6</v>
       </c>
       <c r="D37" s="7" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="E37" s="8">
         <v>600</v>
@@ -2436,14 +2455,14 @@
     </row>
     <row r="38" customHeight="1" spans="1:6">
       <c r="A38" s="7" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="B38" s="7"/>
       <c r="C38" s="7" t="s">
         <v>6</v>
       </c>
       <c r="D38" s="7" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="E38" s="8">
         <v>600</v>
@@ -2452,14 +2471,14 @@
     </row>
     <row r="39" customHeight="1" spans="1:6">
       <c r="A39" s="7" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="B39" s="7"/>
       <c r="C39" s="7" t="s">
         <v>6</v>
       </c>
       <c r="D39" s="7" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="E39" s="8">
         <v>32</v>
@@ -2476,7 +2495,7 @@
     </row>
     <row r="41" customHeight="1" spans="1:6">
       <c r="A41" s="5" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="B41" s="5"/>
       <c r="C41" s="5"/>
@@ -2486,17 +2505,17 @@
     </row>
     <row r="42" customHeight="1" spans="1:6">
       <c r="A42" s="7" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="B42" s="7"/>
       <c r="C42" s="7" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="D42" s="7" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="E42" s="8" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="F42" s="7"/>
     </row>

--- a/数据表/Datas/GlobalConfig_全局配置.xlsx
+++ b/数据表/Datas/GlobalConfig_全局配置.xlsx
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="115" uniqueCount="86">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="127" uniqueCount="94">
   <si>
     <t>##var#column</t>
   </si>
@@ -86,20 +86,6 @@
     </r>
   </si>
   <si>
-    <t>extractionRevealTimeMs</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF202020"/>
-        <rFont val="微软雅黑"/>
-        <charset val="134"/>
-      </rPr>
-      <t>小地图标记撤离点的时间，毫秒</t>
-    </r>
-  </si>
-  <si>
     <t>mapDefinitionPath</t>
   </si>
   <si>
@@ -286,6 +272,40 @@
       </rPr>
       <t>局内道具实体</t>
     </r>
+  </si>
+  <si>
+    <t>LootRangeMinRadius</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF202020"/>
+        <rFont val="微软雅黑"/>
+        <charset val="134"/>
+      </rPr>
+      <t>资源点道具掉落最小半径，毫米</t>
+    </r>
+  </si>
+  <si>
+    <t>LootRangeMaxRadius</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF202020"/>
+        <rFont val="微软雅黑"/>
+        <charset val="134"/>
+      </rPr>
+      <t>资源点道具掉落最大半径，毫米</t>
+    </r>
+  </si>
+  <si>
+    <t>evacuateTimeMs</t>
+  </si>
+  <si>
+    <t>撤离时间，毫秒</t>
   </si>
   <si>
     <r>
@@ -325,20 +345,6 @@
     </r>
   </si>
   <si>
-    <t>enemyFrontViewAngle</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF202020"/>
-        <rFont val="微软雅黑"/>
-        <charset val="134"/>
-      </rPr>
-      <t>敌人正面视野角度</t>
-    </r>
-  </si>
-  <si>
     <t>alertMax</t>
   </si>
   <si>
@@ -350,6 +356,48 @@
         <charset val="134"/>
       </rPr>
       <t>警惕值满值</t>
+    </r>
+  </si>
+  <si>
+    <t>chaseSpeed</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF202020"/>
+        <rFont val="微软雅黑"/>
+        <charset val="134"/>
+      </rPr>
+      <t>追逐速度</t>
+    </r>
+  </si>
+  <si>
+    <t>patrolSpeed</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF202020"/>
+        <rFont val="微软雅黑"/>
+        <charset val="134"/>
+      </rPr>
+      <t>巡逻速度</t>
+    </r>
+  </si>
+  <si>
+    <t>playerSpeed</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF202020"/>
+        <rFont val="微软雅黑"/>
+        <charset val="134"/>
+      </rPr>
+      <t>玩家速度</t>
     </r>
   </si>
   <si>
@@ -744,6 +792,12 @@
       <charset val="134"/>
     </font>
     <font>
+      <sz val="12"/>
+      <color rgb="FF202020"/>
+      <name val="微软雅黑"/>
+      <charset val="134"/>
+    </font>
+    <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
@@ -893,12 +947,6 @@
       <name val="Calibri"/>
       <charset val="0"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="12"/>
-      <color rgb="FF202020"/>
-      <name val="微软雅黑"/>
-      <charset val="134"/>
     </font>
     <font>
       <sz val="12"/>
@@ -1253,153 +1301,153 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="43" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="7" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="49"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="49" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="49" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1425,6 +1473,9 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="50">
@@ -1897,7 +1948,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:F42"/>
+  <dimension ref="A1:F46"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="20" customHeight="1" outlineLevelCol="5"/>
   <cols>
     <col min="1" max="1" width="34" style="1" customWidth="1"/>
@@ -1959,29 +2010,29 @@
       </c>
       <c r="B4" s="7"/>
       <c r="C4" s="7" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="D4" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="E4" s="8">
-        <v>1200000</v>
+        <v>10</v>
+      </c>
+      <c r="E4" s="8" t="s">
+        <v>11</v>
       </c>
       <c r="F4" s="7"/>
     </row>
     <row r="5" customHeight="1" spans="1:6">
       <c r="A5" s="7" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B5" s="7"/>
       <c r="C5" s="7" t="s">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="D5" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="E5" s="8" t="s">
         <v>13</v>
+      </c>
+      <c r="E5" s="8">
+        <v>2000</v>
       </c>
       <c r="F5" s="7"/>
     </row>
@@ -1991,107 +2042,107 @@
       </c>
       <c r="B6" s="7"/>
       <c r="C6" s="7" t="s">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="D6" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="E6" s="8">
-        <v>2000</v>
+        <v>16</v>
+      </c>
+      <c r="E6" s="8" t="s">
+        <v>17</v>
       </c>
       <c r="F6" s="7"/>
     </row>
     <row r="7" customHeight="1" spans="1:6">
       <c r="A7" s="7" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="B7" s="7"/>
       <c r="C7" s="7" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="D7" s="7" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E7" s="8" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F7" s="7"/>
     </row>
     <row r="8" customHeight="1" spans="1:6">
       <c r="A8" s="7" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B8" s="7"/>
       <c r="C8" s="7" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="D8" s="7" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E8" s="8" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F8" s="7"/>
     </row>
     <row r="9" customHeight="1" spans="1:6">
-      <c r="A9" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="B9" s="7"/>
+      <c r="A9" s="1" t="s">
+        <v>24</v>
+      </c>
       <c r="C9" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="D9" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="E9" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="D9" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="F9" s="7"/>
+      <c r="E9" s="9" t="s">
+        <v>26</v>
+      </c>
     </row>
     <row r="10" customHeight="1" spans="1:6">
-      <c r="A10" s="1" t="s">
-        <v>26</v>
-      </c>
+      <c r="A10" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="B10" s="7"/>
       <c r="C10" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="D10" s="1" t="s">
-        <v>27</v>
+        <v>15</v>
+      </c>
+      <c r="D10" s="7" t="s">
+        <v>28</v>
       </c>
       <c r="E10" s="9" t="s">
-        <v>28</v>
-      </c>
+        <v>29</v>
+      </c>
+      <c r="F10" s="7"/>
     </row>
     <row r="11" customHeight="1" spans="1:6">
       <c r="A11" s="7" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B11" s="7"/>
       <c r="C11" s="7" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="D11" s="7" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E11" s="9" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F11" s="7"/>
     </row>
     <row r="12" customHeight="1" spans="1:6">
       <c r="A12" s="7" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B12" s="7"/>
       <c r="C12" s="7" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="D12" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="E12" s="8" t="s">
         <v>33</v>
-      </c>
-      <c r="E12" s="9" t="s">
-        <v>34</v>
       </c>
       <c r="F12" s="7"/>
     </row>
@@ -2101,65 +2152,65 @@
       </c>
       <c r="B13" s="7"/>
       <c r="C13" s="7" t="s">
-        <v>17</v>
+        <v>6</v>
       </c>
       <c r="D13" s="7" t="s">
         <v>36</v>
       </c>
-      <c r="E13" s="8" t="s">
-        <v>35</v>
+      <c r="E13" s="8">
+        <v>1000</v>
       </c>
       <c r="F13" s="7"/>
     </row>
     <row r="14" customHeight="1" spans="1:6">
-      <c r="A14" s="7"/>
+      <c r="A14" s="7" t="s">
+        <v>37</v>
+      </c>
       <c r="B14" s="7"/>
-      <c r="C14" s="7"/>
-      <c r="D14" s="7"/>
-      <c r="E14" s="8"/>
+      <c r="C14" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="D14" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="E14" s="8">
+        <v>2500</v>
+      </c>
       <c r="F14" s="7"/>
     </row>
     <row r="15" customHeight="1" spans="1:6">
-      <c r="A15" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B15" s="5"/>
-      <c r="C15" s="5"/>
-      <c r="D15" s="5"/>
-      <c r="E15" s="6"/>
-      <c r="F15" s="5"/>
+      <c r="A15" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="B15" s="7"/>
+      <c r="C15" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="D15" s="10" t="s">
+        <v>40</v>
+      </c>
+      <c r="E15" s="8">
+        <v>5000</v>
+      </c>
+      <c r="F15" s="7"/>
     </row>
     <row r="16" customHeight="1" spans="1:6">
-      <c r="A16" s="7" t="s">
-        <v>38</v>
-      </c>
+      <c r="A16" s="7"/>
       <c r="B16" s="7"/>
-      <c r="C16" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="D16" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="E16" s="8">
-        <v>3000</v>
-      </c>
+      <c r="C16" s="7"/>
+      <c r="D16" s="7"/>
+      <c r="E16" s="8"/>
       <c r="F16" s="7"/>
     </row>
     <row r="17" customHeight="1" spans="1:6">
-      <c r="A17" s="7" t="s">
-        <v>40</v>
-      </c>
-      <c r="B17" s="7"/>
-      <c r="C17" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="D17" s="7" t="s">
+      <c r="A17" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="E17" s="8">
-        <v>180</v>
-      </c>
-      <c r="F17" s="7"/>
+      <c r="B17" s="5"/>
+      <c r="C17" s="5"/>
+      <c r="D17" s="5"/>
+      <c r="E17" s="6"/>
+      <c r="F17" s="5"/>
     </row>
     <row r="18" customHeight="1" spans="1:6">
       <c r="A18" s="7" t="s">
@@ -2173,91 +2224,91 @@
         <v>43</v>
       </c>
       <c r="E18" s="8">
+        <v>3000</v>
+      </c>
+      <c r="F18" s="7"/>
+    </row>
+    <row r="19" customHeight="1" spans="1:6">
+      <c r="A19" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="B19" s="7"/>
+      <c r="C19" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="D19" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="E19" s="8">
         <v>1000</v>
       </c>
-      <c r="F18" s="7"/>
-    </row>
-    <row r="19" customHeight="1" spans="1:6">
-      <c r="A19" s="7"/>
-      <c r="B19" s="7"/>
-      <c r="C19" s="7"/>
-      <c r="D19" s="7"/>
-      <c r="E19" s="8"/>
       <c r="F19" s="7"/>
     </row>
     <row r="20" customHeight="1" spans="1:6">
-      <c r="A20" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="B20" s="5"/>
-      <c r="C20" s="5"/>
-      <c r="D20" s="5"/>
-      <c r="E20" s="6"/>
-      <c r="F20" s="5"/>
+      <c r="A20" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="B20" s="7"/>
+      <c r="C20" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="D20" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="E20" s="8">
+        <v>4000</v>
+      </c>
+      <c r="F20" s="7"/>
     </row>
     <row r="21" customHeight="1" spans="1:6">
       <c r="A21" s="7" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="B21" s="7"/>
       <c r="C21" s="7" t="s">
         <v>6</v>
       </c>
       <c r="D21" s="7" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="E21" s="8">
-        <v>120</v>
+        <v>3000</v>
       </c>
       <c r="F21" s="7"/>
     </row>
     <row r="22" customHeight="1" spans="1:6">
       <c r="A22" s="7" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="B22" s="7"/>
       <c r="C22" s="7" t="s">
         <v>6</v>
       </c>
       <c r="D22" s="7" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="E22" s="8">
-        <v>30</v>
+        <v>4500</v>
       </c>
       <c r="F22" s="7"/>
     </row>
     <row r="23" customHeight="1" spans="1:6">
-      <c r="A23" s="7" t="s">
-        <v>49</v>
-      </c>
+      <c r="A23" s="7"/>
       <c r="B23" s="7"/>
-      <c r="C23" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="D23" s="7" t="s">
-        <v>50</v>
-      </c>
-      <c r="E23" s="8">
-        <v>5</v>
-      </c>
+      <c r="C23" s="7"/>
+      <c r="D23" s="7"/>
+      <c r="E23" s="8"/>
       <c r="F23" s="7"/>
     </row>
     <row r="24" customHeight="1" spans="1:6">
-      <c r="A24" s="7" t="s">
-        <v>51</v>
-      </c>
-      <c r="B24" s="7"/>
-      <c r="C24" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="D24" s="7" t="s">
+      <c r="A24" s="5" t="s">
         <v>52</v>
       </c>
-      <c r="E24" s="8">
-        <v>1</v>
-      </c>
-      <c r="F24" s="7"/>
+      <c r="B24" s="5"/>
+      <c r="C24" s="5"/>
+      <c r="D24" s="5"/>
+      <c r="E24" s="6"/>
+      <c r="F24" s="5"/>
     </row>
     <row r="25" customHeight="1" spans="1:6">
       <c r="A25" s="7" t="s">
@@ -2271,7 +2322,7 @@
         <v>54</v>
       </c>
       <c r="E25" s="8">
-        <v>4</v>
+        <v>120</v>
       </c>
       <c r="F25" s="7"/>
     </row>
@@ -2287,153 +2338,153 @@
         <v>56</v>
       </c>
       <c r="E26" s="8">
-        <v>4</v>
+        <v>30</v>
       </c>
       <c r="F26" s="7"/>
     </row>
     <row r="27" customHeight="1" spans="1:6">
-      <c r="A27" s="7"/>
+      <c r="A27" s="7" t="s">
+        <v>57</v>
+      </c>
       <c r="B27" s="7"/>
-      <c r="C27" s="7"/>
-      <c r="D27" s="7"/>
-      <c r="E27" s="8"/>
+      <c r="C27" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="D27" s="7" t="s">
+        <v>58</v>
+      </c>
+      <c r="E27" s="8">
+        <v>5</v>
+      </c>
       <c r="F27" s="7"/>
     </row>
     <row r="28" customHeight="1" spans="1:6">
-      <c r="A28" s="5" t="s">
-        <v>57</v>
-      </c>
-      <c r="B28" s="5"/>
-      <c r="C28" s="5"/>
-      <c r="D28" s="5"/>
-      <c r="E28" s="6"/>
-      <c r="F28" s="5"/>
+      <c r="A28" s="7" t="s">
+        <v>59</v>
+      </c>
+      <c r="B28" s="7"/>
+      <c r="C28" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="D28" s="7" t="s">
+        <v>60</v>
+      </c>
+      <c r="E28" s="8">
+        <v>1</v>
+      </c>
+      <c r="F28" s="7"/>
     </row>
     <row r="29" customHeight="1" spans="1:6">
       <c r="A29" s="7" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="B29" s="7"/>
       <c r="C29" s="7" t="s">
         <v>6</v>
       </c>
       <c r="D29" s="7" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="E29" s="8">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F29" s="7"/>
     </row>
     <row r="30" customHeight="1" spans="1:6">
       <c r="A30" s="7" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="B30" s="7"/>
       <c r="C30" s="7" t="s">
         <v>6</v>
       </c>
       <c r="D30" s="7" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="E30" s="8">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F30" s="7"/>
     </row>
     <row r="31" customHeight="1" spans="1:6">
-      <c r="A31" s="7" t="s">
-        <v>62</v>
-      </c>
+      <c r="A31" s="7"/>
       <c r="B31" s="7"/>
-      <c r="C31" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="D31" s="7" t="s">
-        <v>63</v>
-      </c>
-      <c r="E31" s="8">
-        <v>500</v>
-      </c>
+      <c r="C31" s="7"/>
+      <c r="D31" s="7"/>
+      <c r="E31" s="8"/>
       <c r="F31" s="7"/>
     </row>
     <row r="32" customHeight="1" spans="1:6">
-      <c r="A32" s="7" t="s">
-        <v>64</v>
-      </c>
-      <c r="B32" s="7"/>
-      <c r="C32" s="7" t="s">
+      <c r="A32" s="5" t="s">
         <v>65</v>
       </c>
-      <c r="D32" s="7" t="s">
-        <v>66</v>
-      </c>
-      <c r="E32" s="8" t="b">
-        <v>0</v>
-      </c>
-      <c r="F32" s="7"/>
+      <c r="B32" s="5"/>
+      <c r="C32" s="5"/>
+      <c r="D32" s="5"/>
+      <c r="E32" s="6"/>
+      <c r="F32" s="5"/>
     </row>
     <row r="33" customHeight="1" spans="1:6">
       <c r="A33" s="7" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B33" s="7"/>
       <c r="C33" s="7" t="s">
-        <v>65</v>
+        <v>6</v>
       </c>
       <c r="D33" s="7" t="s">
-        <v>68</v>
-      </c>
-      <c r="E33" s="8" t="b">
+        <v>67</v>
+      </c>
+      <c r="E33" s="8">
         <v>1</v>
       </c>
       <c r="F33" s="7"/>
     </row>
     <row r="34" customHeight="1" spans="1:6">
       <c r="A34" s="7" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B34" s="7"/>
       <c r="C34" s="7" t="s">
-        <v>65</v>
+        <v>6</v>
       </c>
       <c r="D34" s="7" t="s">
-        <v>70</v>
-      </c>
-      <c r="E34" s="8" t="b">
-        <v>0</v>
+        <v>69</v>
+      </c>
+      <c r="E34" s="8">
+        <v>1</v>
       </c>
       <c r="F34" s="7"/>
     </row>
     <row r="35" customHeight="1" spans="1:6">
       <c r="A35" s="7" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B35" s="7"/>
       <c r="C35" s="7" t="s">
-        <v>65</v>
+        <v>6</v>
       </c>
       <c r="D35" s="7" t="s">
-        <v>72</v>
-      </c>
-      <c r="E35" s="8" t="b">
-        <v>1</v>
+        <v>71</v>
+      </c>
+      <c r="E35" s="8">
+        <v>500</v>
       </c>
       <c r="F35" s="7"/>
     </row>
     <row r="36" customHeight="1" spans="1:6">
       <c r="A36" s="7" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B36" s="7"/>
       <c r="C36" s="7" t="s">
-        <v>6</v>
+        <v>73</v>
       </c>
       <c r="D36" s="7" t="s">
         <v>74</v>
       </c>
-      <c r="E36" s="8">
-        <v>600</v>
+      <c r="E36" s="8" t="b">
+        <v>0</v>
       </c>
       <c r="F36" s="7"/>
     </row>
@@ -2443,13 +2494,13 @@
       </c>
       <c r="B37" s="7"/>
       <c r="C37" s="7" t="s">
-        <v>6</v>
+        <v>73</v>
       </c>
       <c r="D37" s="7" t="s">
         <v>76</v>
       </c>
-      <c r="E37" s="8">
-        <v>600</v>
+      <c r="E37" s="8" t="b">
+        <v>1</v>
       </c>
       <c r="F37" s="7"/>
     </row>
@@ -2459,13 +2510,13 @@
       </c>
       <c r="B38" s="7"/>
       <c r="C38" s="7" t="s">
-        <v>6</v>
+        <v>73</v>
       </c>
       <c r="D38" s="7" t="s">
         <v>78</v>
       </c>
-      <c r="E38" s="8">
-        <v>600</v>
+      <c r="E38" s="8" t="b">
+        <v>0</v>
       </c>
       <c r="F38" s="7"/>
     </row>
@@ -2475,49 +2526,113 @@
       </c>
       <c r="B39" s="7"/>
       <c r="C39" s="7" t="s">
-        <v>6</v>
+        <v>73</v>
       </c>
       <c r="D39" s="7" t="s">
         <v>80</v>
       </c>
-      <c r="E39" s="8">
-        <v>32</v>
+      <c r="E39" s="8" t="b">
+        <v>1</v>
       </c>
       <c r="F39" s="7"/>
     </row>
     <row r="40" customHeight="1" spans="1:6">
-      <c r="A40" s="7"/>
+      <c r="A40" s="7" t="s">
+        <v>81</v>
+      </c>
       <c r="B40" s="7"/>
-      <c r="C40" s="7"/>
-      <c r="D40" s="7"/>
-      <c r="E40" s="8"/>
+      <c r="C40" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="D40" s="7" t="s">
+        <v>82</v>
+      </c>
+      <c r="E40" s="8">
+        <v>600</v>
+      </c>
       <c r="F40" s="7"/>
     </row>
     <row r="41" customHeight="1" spans="1:6">
-      <c r="A41" s="5" t="s">
-        <v>81</v>
-      </c>
-      <c r="B41" s="5"/>
-      <c r="C41" s="5"/>
-      <c r="D41" s="5"/>
-      <c r="E41" s="6"/>
-      <c r="F41" s="5"/>
+      <c r="A41" s="7" t="s">
+        <v>83</v>
+      </c>
+      <c r="B41" s="7"/>
+      <c r="C41" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="D41" s="7" t="s">
+        <v>84</v>
+      </c>
+      <c r="E41" s="8">
+        <v>600</v>
+      </c>
+      <c r="F41" s="7"/>
     </row>
     <row r="42" customHeight="1" spans="1:6">
       <c r="A42" s="7" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="B42" s="7"/>
       <c r="C42" s="7" t="s">
-        <v>83</v>
+        <v>6</v>
       </c>
       <c r="D42" s="7" t="s">
-        <v>84</v>
-      </c>
-      <c r="E42" s="8" t="s">
-        <v>85</v>
+        <v>86</v>
+      </c>
+      <c r="E42" s="8">
+        <v>600</v>
       </c>
       <c r="F42" s="7"/>
+    </row>
+    <row r="43" customHeight="1" spans="1:6">
+      <c r="A43" s="7" t="s">
+        <v>87</v>
+      </c>
+      <c r="B43" s="7"/>
+      <c r="C43" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="D43" s="7" t="s">
+        <v>88</v>
+      </c>
+      <c r="E43" s="8">
+        <v>32</v>
+      </c>
+      <c r="F43" s="7"/>
+    </row>
+    <row r="44" customHeight="1" spans="1:6">
+      <c r="A44" s="7"/>
+      <c r="B44" s="7"/>
+      <c r="C44" s="7"/>
+      <c r="D44" s="7"/>
+      <c r="E44" s="8"/>
+      <c r="F44" s="7"/>
+    </row>
+    <row r="45" customHeight="1" spans="1:6">
+      <c r="A45" s="5" t="s">
+        <v>89</v>
+      </c>
+      <c r="B45" s="5"/>
+      <c r="C45" s="5"/>
+      <c r="D45" s="5"/>
+      <c r="E45" s="6"/>
+      <c r="F45" s="5"/>
+    </row>
+    <row r="46" customHeight="1" spans="1:6">
+      <c r="A46" s="7" t="s">
+        <v>90</v>
+      </c>
+      <c r="B46" s="7"/>
+      <c r="C46" s="7" t="s">
+        <v>91</v>
+      </c>
+      <c r="D46" s="7" t="s">
+        <v>92</v>
+      </c>
+      <c r="E46" s="8" t="s">
+        <v>93</v>
+      </c>
+      <c r="F46" s="7"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/数据表/Datas/GlobalConfig_全局配置.xlsx
+++ b/数据表/Datas/GlobalConfig_全局配置.xlsx
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="127" uniqueCount="94">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="159" uniqueCount="116">
   <si>
     <t>##var#column</t>
   </si>
@@ -305,7 +305,32 @@
     <t>evacuateTimeMs</t>
   </si>
   <si>
-    <t>撤离时间，毫秒</t>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF202020"/>
+        <rFont val="微软雅黑"/>
+        <charset val="134"/>
+      </rPr>
+      <t>撤离时间，毫秒</t>
+    </r>
+  </si>
+  <si>
+    <t>WorldFloatTextEntity</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF202020"/>
+        <rFont val="微软雅黑"/>
+        <charset val="134"/>
+      </rPr>
+      <t>世界漂浮文本实体</t>
+    </r>
+  </si>
+  <si>
+    <t>WorldFloatText</t>
   </si>
   <si>
     <r>
@@ -750,6 +775,174 @@
   </si>
   <si>
     <t>1001,1002,1003,1004</t>
+  </si>
+  <si>
+    <r>
+      <t>##======== UI</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF375623"/>
+        <rFont val="微软雅黑"/>
+        <charset val="134"/>
+      </rPr>
+      <t>设置</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF375623"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> ==========</t>
+    </r>
+  </si>
+  <si>
+    <t>LobbySelectionMarkerMoveDurationMs</t>
+  </si>
+  <si>
+    <r>
+      <t>LobbyForm</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="微软雅黑"/>
+        <charset val="134"/>
+      </rPr>
+      <t>选中标记移动动画持续时间，毫秒</t>
+    </r>
+  </si>
+  <si>
+    <t>BattleResultDisplayDelayMs</t>
+  </si>
+  <si>
+    <r>
+      <t>BattleForm</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="微软雅黑"/>
+        <charset val="134"/>
+      </rPr>
+      <t>结算等待时间，毫秒</t>
+    </r>
+  </si>
+  <si>
+    <t>BattleInDurationMs</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="微软雅黑"/>
+        <charset val="134"/>
+      </rPr>
+      <t>战斗入场动画时间，毫秒</t>
+    </r>
+  </si>
+  <si>
+    <t>BattleInScale</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="微软雅黑"/>
+        <charset val="134"/>
+      </rPr>
+      <t>战斗入场缩放系数</t>
+    </r>
+  </si>
+  <si>
+    <t>BattleInPunchScale</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="微软雅黑"/>
+        <charset val="134"/>
+      </rPr>
+      <t>战斗入场</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
+      <t>Punch</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="微软雅黑"/>
+        <charset val="134"/>
+      </rPr>
+      <t>操作缩放系数</t>
+    </r>
+  </si>
+  <si>
+    <t>BattleOutDurationMs</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="微软雅黑"/>
+        <charset val="134"/>
+      </rPr>
+      <t>战斗离场动画时间，毫秒</t>
+    </r>
+  </si>
+  <si>
+    <t>BattleActorCardOutPixels</t>
+  </si>
+  <si>
+    <r>
+      <t>BattleActorCard</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="微软雅黑"/>
+        <charset val="134"/>
+      </rPr>
+      <t>战斗离场动画跳跃距离，像素</t>
+    </r>
+  </si>
+  <si>
+    <t>BattleEnemyCardOutPixels</t>
+  </si>
+  <si>
+    <r>
+      <t>EnemyCard</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="微软雅黑"/>
+        <charset val="134"/>
+      </rPr>
+      <t>战斗离场动画上浮距离，像素</t>
+    </r>
+  </si>
+  <si>
+    <t>BattleInMoveIntervalMs</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="微软雅黑"/>
+        <charset val="134"/>
+      </rPr>
+      <t>战斗入场卡片动画开始间隔</t>
+    </r>
   </si>
 </sst>
 </file>
@@ -789,12 +982,6 @@
       <sz val="12"/>
       <color rgb="FF202020"/>
       <name val="Consolas"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="12"/>
-      <color rgb="FF202020"/>
-      <name val="微软雅黑"/>
       <charset val="134"/>
     </font>
     <font>
@@ -950,6 +1137,12 @@
     </font>
     <font>
       <sz val="12"/>
+      <color rgb="FF202020"/>
+      <name val="微软雅黑"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="12"/>
       <name val="微软雅黑"/>
       <charset val="134"/>
     </font>
@@ -1301,153 +1494,153 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="43" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="6" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="7" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="49"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="49" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="49" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1473,9 +1666,6 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="50">
@@ -1948,13 +2138,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:F46"/>
+  <dimension ref="A1:F60"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="20" customHeight="1" outlineLevelCol="5"/>
   <cols>
-    <col min="1" max="1" width="34" style="1" customWidth="1"/>
+    <col min="1" max="1" width="40.25" style="1" customWidth="1"/>
     <col min="2" max="2" width="12.0083333333333" style="1" customWidth="1"/>
     <col min="3" max="3" width="32.6666666666667" style="1" customWidth="1"/>
-    <col min="4" max="4" width="39.825" style="1" customWidth="1"/>
+    <col min="4" max="4" width="44.3333333333333" style="1" customWidth="1"/>
     <col min="5" max="5" width="29.2833333333333" style="2" customWidth="1"/>
     <col min="6" max="6" width="28" style="1" customWidth="1"/>
     <col min="7" max="16384" width="9" style="1"/>
@@ -2186,7 +2376,7 @@
       <c r="C15" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="D15" s="10" t="s">
+      <c r="D15" s="7" t="s">
         <v>40</v>
       </c>
       <c r="E15" s="8">
@@ -2195,211 +2385,211 @@
       <c r="F15" s="7"/>
     </row>
     <row r="16" customHeight="1" spans="1:6">
-      <c r="A16" s="7"/>
+      <c r="A16" s="7" t="s">
+        <v>41</v>
+      </c>
       <c r="B16" s="7"/>
-      <c r="C16" s="7"/>
-      <c r="D16" s="7"/>
-      <c r="E16" s="8"/>
+      <c r="C16" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="D16" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="E16" s="8" t="s">
+        <v>43</v>
+      </c>
       <c r="F16" s="7"/>
     </row>
     <row r="17" customHeight="1" spans="1:6">
-      <c r="A17" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="B17" s="5"/>
-      <c r="C17" s="5"/>
-      <c r="D17" s="5"/>
-      <c r="E17" s="6"/>
-      <c r="F17" s="5"/>
+      <c r="A17" s="7"/>
+      <c r="B17" s="7"/>
+      <c r="C17" s="7"/>
+      <c r="D17" s="7"/>
+      <c r="E17" s="8"/>
+      <c r="F17" s="7"/>
     </row>
     <row r="18" customHeight="1" spans="1:6">
-      <c r="A18" s="7" t="s">
-        <v>42</v>
-      </c>
-      <c r="B18" s="7"/>
-      <c r="C18" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="D18" s="7" t="s">
-        <v>43</v>
-      </c>
-      <c r="E18" s="8">
-        <v>3000</v>
-      </c>
-      <c r="F18" s="7"/>
+      <c r="A18" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="B18" s="5"/>
+      <c r="C18" s="5"/>
+      <c r="D18" s="5"/>
+      <c r="E18" s="6"/>
+      <c r="F18" s="5"/>
     </row>
     <row r="19" customHeight="1" spans="1:6">
       <c r="A19" s="7" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B19" s="7"/>
       <c r="C19" s="7" t="s">
         <v>6</v>
       </c>
       <c r="D19" s="7" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="E19" s="8">
-        <v>1000</v>
+        <v>3000</v>
       </c>
       <c r="F19" s="7"/>
     </row>
     <row r="20" customHeight="1" spans="1:6">
       <c r="A20" s="7" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B20" s="7"/>
       <c r="C20" s="7" t="s">
         <v>6</v>
       </c>
       <c r="D20" s="7" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="E20" s="8">
-        <v>4000</v>
+        <v>1000</v>
       </c>
       <c r="F20" s="7"/>
     </row>
     <row r="21" customHeight="1" spans="1:6">
       <c r="A21" s="7" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B21" s="7"/>
       <c r="C21" s="7" t="s">
         <v>6</v>
       </c>
       <c r="D21" s="7" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="E21" s="8">
-        <v>3000</v>
+        <v>4000</v>
       </c>
       <c r="F21" s="7"/>
     </row>
     <row r="22" customHeight="1" spans="1:6">
       <c r="A22" s="7" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B22" s="7"/>
       <c r="C22" s="7" t="s">
         <v>6</v>
       </c>
       <c r="D22" s="7" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E22" s="8">
+        <v>3000</v>
+      </c>
+      <c r="F22" s="7"/>
+    </row>
+    <row r="23" customHeight="1" spans="1:6">
+      <c r="A23" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="B23" s="7"/>
+      <c r="C23" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="D23" s="7" t="s">
+        <v>54</v>
+      </c>
+      <c r="E23" s="8">
         <v>4500</v>
       </c>
-      <c r="F22" s="7"/>
-    </row>
-    <row r="23" customHeight="1" spans="1:6">
-      <c r="A23" s="7"/>
-      <c r="B23" s="7"/>
-      <c r="C23" s="7"/>
-      <c r="D23" s="7"/>
-      <c r="E23" s="8"/>
       <c r="F23" s="7"/>
     </row>
     <row r="24" customHeight="1" spans="1:6">
-      <c r="A24" s="5" t="s">
-        <v>52</v>
-      </c>
-      <c r="B24" s="5"/>
-      <c r="C24" s="5"/>
-      <c r="D24" s="5"/>
-      <c r="E24" s="6"/>
-      <c r="F24" s="5"/>
+      <c r="A24" s="7"/>
+      <c r="B24" s="7"/>
+      <c r="C24" s="7"/>
+      <c r="D24" s="7"/>
+      <c r="E24" s="8"/>
+      <c r="F24" s="7"/>
     </row>
     <row r="25" customHeight="1" spans="1:6">
-      <c r="A25" s="7" t="s">
-        <v>53</v>
-      </c>
-      <c r="B25" s="7"/>
-      <c r="C25" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="D25" s="7" t="s">
-        <v>54</v>
-      </c>
-      <c r="E25" s="8">
-        <v>120</v>
-      </c>
-      <c r="F25" s="7"/>
+      <c r="A25" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="B25" s="5"/>
+      <c r="C25" s="5"/>
+      <c r="D25" s="5"/>
+      <c r="E25" s="6"/>
+      <c r="F25" s="5"/>
     </row>
     <row r="26" customHeight="1" spans="1:6">
       <c r="A26" s="7" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B26" s="7"/>
       <c r="C26" s="7" t="s">
         <v>6</v>
       </c>
       <c r="D26" s="7" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E26" s="8">
-        <v>30</v>
+        <v>120</v>
       </c>
       <c r="F26" s="7"/>
     </row>
     <row r="27" customHeight="1" spans="1:6">
       <c r="A27" s="7" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B27" s="7"/>
       <c r="C27" s="7" t="s">
         <v>6</v>
       </c>
       <c r="D27" s="7" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E27" s="8">
-        <v>5</v>
+        <v>30</v>
       </c>
       <c r="F27" s="7"/>
     </row>
     <row r="28" customHeight="1" spans="1:6">
       <c r="A28" s="7" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B28" s="7"/>
       <c r="C28" s="7" t="s">
         <v>6</v>
       </c>
       <c r="D28" s="7" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E28" s="8">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F28" s="7"/>
     </row>
     <row r="29" customHeight="1" spans="1:6">
       <c r="A29" s="7" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B29" s="7"/>
       <c r="C29" s="7" t="s">
         <v>6</v>
       </c>
       <c r="D29" s="7" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E29" s="8">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F29" s="7"/>
     </row>
     <row r="30" customHeight="1" spans="1:6">
       <c r="A30" s="7" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B30" s="7"/>
       <c r="C30" s="7" t="s">
         <v>6</v>
       </c>
       <c r="D30" s="7" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="E30" s="8">
         <v>4</v>
@@ -2407,49 +2597,49 @@
       <c r="F30" s="7"/>
     </row>
     <row r="31" customHeight="1" spans="1:6">
-      <c r="A31" s="7"/>
+      <c r="A31" s="7" t="s">
+        <v>66</v>
+      </c>
       <c r="B31" s="7"/>
-      <c r="C31" s="7"/>
-      <c r="D31" s="7"/>
-      <c r="E31" s="8"/>
+      <c r="C31" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="D31" s="7" t="s">
+        <v>67</v>
+      </c>
+      <c r="E31" s="8">
+        <v>4</v>
+      </c>
       <c r="F31" s="7"/>
     </row>
     <row r="32" customHeight="1" spans="1:6">
-      <c r="A32" s="5" t="s">
-        <v>65</v>
-      </c>
-      <c r="B32" s="5"/>
-      <c r="C32" s="5"/>
-      <c r="D32" s="5"/>
-      <c r="E32" s="6"/>
-      <c r="F32" s="5"/>
+      <c r="A32" s="7"/>
+      <c r="B32" s="7"/>
+      <c r="C32" s="7"/>
+      <c r="D32" s="7"/>
+      <c r="E32" s="8"/>
+      <c r="F32" s="7"/>
     </row>
     <row r="33" customHeight="1" spans="1:6">
-      <c r="A33" s="7" t="s">
-        <v>66</v>
-      </c>
-      <c r="B33" s="7"/>
-      <c r="C33" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="D33" s="7" t="s">
-        <v>67</v>
-      </c>
-      <c r="E33" s="8">
-        <v>1</v>
-      </c>
-      <c r="F33" s="7"/>
+      <c r="A33" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="B33" s="5"/>
+      <c r="C33" s="5"/>
+      <c r="D33" s="5"/>
+      <c r="E33" s="6"/>
+      <c r="F33" s="5"/>
     </row>
     <row r="34" customHeight="1" spans="1:6">
       <c r="A34" s="7" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B34" s="7"/>
       <c r="C34" s="7" t="s">
         <v>6</v>
       </c>
       <c r="D34" s="7" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="E34" s="8">
         <v>1</v>
@@ -2458,33 +2648,33 @@
     </row>
     <row r="35" customHeight="1" spans="1:6">
       <c r="A35" s="7" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B35" s="7"/>
       <c r="C35" s="7" t="s">
         <v>6</v>
       </c>
       <c r="D35" s="7" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="E35" s="8">
-        <v>500</v>
+        <v>1</v>
       </c>
       <c r="F35" s="7"/>
     </row>
     <row r="36" customHeight="1" spans="1:6">
       <c r="A36" s="7" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="B36" s="7"/>
       <c r="C36" s="7" t="s">
-        <v>73</v>
+        <v>6</v>
       </c>
       <c r="D36" s="7" t="s">
         <v>74</v>
       </c>
-      <c r="E36" s="8" t="b">
-        <v>0</v>
+      <c r="E36" s="8">
+        <v>500</v>
       </c>
       <c r="F36" s="7"/>
     </row>
@@ -2494,74 +2684,74 @@
       </c>
       <c r="B37" s="7"/>
       <c r="C37" s="7" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="D37" s="7" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="E37" s="8" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F37" s="7"/>
     </row>
     <row r="38" customHeight="1" spans="1:6">
       <c r="A38" s="7" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="B38" s="7"/>
       <c r="C38" s="7" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="D38" s="7" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="E38" s="8" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F38" s="7"/>
     </row>
     <row r="39" customHeight="1" spans="1:6">
       <c r="A39" s="7" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="B39" s="7"/>
       <c r="C39" s="7" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="D39" s="7" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="E39" s="8" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F39" s="7"/>
     </row>
     <row r="40" customHeight="1" spans="1:6">
       <c r="A40" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B40" s="7"/>
       <c r="C40" s="7" t="s">
-        <v>6</v>
+        <v>76</v>
       </c>
       <c r="D40" s="7" t="s">
-        <v>82</v>
-      </c>
-      <c r="E40" s="8">
-        <v>600</v>
+        <v>83</v>
+      </c>
+      <c r="E40" s="8" t="b">
+        <v>1</v>
       </c>
       <c r="F40" s="7"/>
     </row>
     <row r="41" customHeight="1" spans="1:6">
       <c r="A41" s="7" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="B41" s="7"/>
       <c r="C41" s="7" t="s">
         <v>6</v>
       </c>
       <c r="D41" s="7" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="E41" s="8">
         <v>600</v>
@@ -2570,14 +2760,14 @@
     </row>
     <row r="42" customHeight="1" spans="1:6">
       <c r="A42" s="7" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B42" s="7"/>
       <c r="C42" s="7" t="s">
         <v>6</v>
       </c>
       <c r="D42" s="7" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="E42" s="8">
         <v>600</v>
@@ -2586,53 +2776,205 @@
     </row>
     <row r="43" customHeight="1" spans="1:6">
       <c r="A43" s="7" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B43" s="7"/>
       <c r="C43" s="7" t="s">
         <v>6</v>
       </c>
       <c r="D43" s="7" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="E43" s="8">
+        <v>600</v>
+      </c>
+      <c r="F43" s="7"/>
+    </row>
+    <row r="44" customHeight="1" spans="1:6">
+      <c r="A44" s="7" t="s">
+        <v>90</v>
+      </c>
+      <c r="B44" s="7"/>
+      <c r="C44" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="D44" s="7" t="s">
+        <v>91</v>
+      </c>
+      <c r="E44" s="8">
         <v>32</v>
       </c>
-      <c r="F43" s="7"/>
-    </row>
-    <row r="44" customHeight="1" spans="1:6">
-      <c r="A44" s="7"/>
-      <c r="B44" s="7"/>
-      <c r="C44" s="7"/>
-      <c r="D44" s="7"/>
-      <c r="E44" s="8"/>
       <c r="F44" s="7"/>
     </row>
     <row r="45" customHeight="1" spans="1:6">
-      <c r="A45" s="5" t="s">
-        <v>89</v>
-      </c>
-      <c r="B45" s="5"/>
-      <c r="C45" s="5"/>
-      <c r="D45" s="5"/>
-      <c r="E45" s="6"/>
-      <c r="F45" s="5"/>
+      <c r="A45" s="7"/>
+      <c r="B45" s="7"/>
+      <c r="C45" s="7"/>
+      <c r="D45" s="7"/>
+      <c r="E45" s="8"/>
+      <c r="F45" s="7"/>
     </row>
     <row r="46" customHeight="1" spans="1:6">
-      <c r="A46" s="7" t="s">
-        <v>90</v>
-      </c>
-      <c r="B46" s="7"/>
-      <c r="C46" s="7" t="s">
-        <v>91</v>
-      </c>
-      <c r="D46" s="7" t="s">
+      <c r="A46" s="5" t="s">
         <v>92</v>
       </c>
-      <c r="E46" s="8" t="s">
+      <c r="B46" s="5"/>
+      <c r="C46" s="5"/>
+      <c r="D46" s="5"/>
+      <c r="E46" s="6"/>
+      <c r="F46" s="5"/>
+    </row>
+    <row r="47" customHeight="1" spans="1:6">
+      <c r="A47" s="7" t="s">
         <v>93</v>
       </c>
-      <c r="F46" s="7"/>
+      <c r="B47" s="7"/>
+      <c r="C47" s="7" t="s">
+        <v>94</v>
+      </c>
+      <c r="D47" s="7" t="s">
+        <v>95</v>
+      </c>
+      <c r="E47" s="8" t="s">
+        <v>96</v>
+      </c>
+      <c r="F47" s="7"/>
+    </row>
+    <row r="51" customHeight="1" spans="1:6">
+      <c r="A51" s="5" t="s">
+        <v>97</v>
+      </c>
+      <c r="B51" s="5"/>
+      <c r="C51" s="5"/>
+      <c r="D51" s="5"/>
+      <c r="E51" s="6"/>
+      <c r="F51" s="5"/>
+    </row>
+    <row r="52" customHeight="1" spans="1:6">
+      <c r="A52" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="C52" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D52" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="E52" s="2">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="53" customHeight="1" spans="1:6">
+      <c r="A53" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="C53" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D53" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="E53" s="2">
+        <v>1500</v>
+      </c>
+    </row>
+    <row r="54" customHeight="1" spans="1:6">
+      <c r="A54" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="C54" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D54" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="E54" s="2">
+        <v>420</v>
+      </c>
+    </row>
+    <row r="55" customHeight="1" spans="1:6">
+      <c r="A55" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="C55" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D55" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="E55" s="2">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="56" customHeight="1" spans="1:6">
+      <c r="A56" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="C56" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D56" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="E56" s="2">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="57" customHeight="1" spans="1:6">
+      <c r="A57" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="C57" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D57" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="E57" s="2">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="58" customHeight="1" spans="1:6">
+      <c r="A58" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="C58" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D58" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="E58" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="59" customHeight="1" spans="1:6">
+      <c r="A59" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="C59" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D59" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="E59" s="2">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="60" customHeight="1" spans="1:6">
+      <c r="A60" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="C60" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D60" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="E60" s="2">
+        <v>80</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/数据表/Datas/GlobalConfig_全局配置.xlsx
+++ b/数据表/Datas/GlobalConfig_全局配置.xlsx
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="159" uniqueCount="116">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="177" uniqueCount="129">
   <si>
     <t>##var#column</t>
   </si>
@@ -243,7 +243,7 @@
     <t>CharacterLeader</t>
   </si>
   <si>
-    <t>CharacterRetinueEntity</t>
+    <t>characterRetinueEntity</t>
   </si>
   <si>
     <r>
@@ -260,21 +260,24 @@
     <t>CharacterRetinue</t>
   </si>
   <si>
+    <t>itemEntity</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF202020"/>
+        <rFont val="微软雅黑"/>
+        <charset val="134"/>
+      </rPr>
+      <t>局内道具实体</t>
+    </r>
+  </si>
+  <si>
     <t>ItemEntity</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF202020"/>
-        <rFont val="微软雅黑"/>
-        <charset val="134"/>
-      </rPr>
-      <t>局内道具实体</t>
-    </r>
-  </si>
-  <si>
-    <t>LootRangeMinRadius</t>
+    <t>lootRangeMinRadius</t>
   </si>
   <si>
     <r>
@@ -288,7 +291,7 @@
     </r>
   </si>
   <si>
-    <t>LootRangeMaxRadius</t>
+    <t>lootRangeMaxRadius</t>
   </si>
   <si>
     <r>
@@ -316,7 +319,7 @@
     </r>
   </si>
   <si>
-    <t>WorldFloatTextEntity</t>
+    <t>worldFloatTextEntity</t>
   </si>
   <si>
     <r>
@@ -463,6 +466,48 @@
     </r>
   </si>
   <si>
+    <t>warehouseFixedColumn</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF202020"/>
+        <rFont val="微软雅黑"/>
+        <charset val="134"/>
+      </rPr>
+      <t>仓库固定列数</t>
+    </r>
+  </si>
+  <si>
+    <t>warehouseSlotSize</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF202020"/>
+        <rFont val="微软雅黑"/>
+        <charset val="134"/>
+      </rPr>
+      <t>仓库格子宽高</t>
+    </r>
+  </si>
+  <si>
+    <t>warehouseSlotGap</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF202020"/>
+        <rFont val="微软雅黑"/>
+        <charset val="134"/>
+      </rPr>
+      <t>仓库格子间距</t>
+    </r>
+  </si>
+  <si>
     <t>backpackSlotCount</t>
   </si>
   <si>
@@ -530,6 +575,20 @@
         <charset val="134"/>
       </rPr>
       <t>敌人队伍人数上限</t>
+    </r>
+  </si>
+  <si>
+    <t>dragHoldThresholdMs</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF202020"/>
+        <rFont val="微软雅黑"/>
+        <charset val="134"/>
+      </rPr>
+      <t>长按拖拽开始阈值</t>
     </r>
   </si>
   <si>
@@ -800,7 +859,7 @@
     </r>
   </si>
   <si>
-    <t>LobbySelectionMarkerMoveDurationMs</t>
+    <t>lobbySelectionMarkerMoveDurationMs</t>
   </si>
   <si>
     <r>
@@ -816,7 +875,7 @@
     </r>
   </si>
   <si>
-    <t>BattleResultDisplayDelayMs</t>
+    <t>battleResultDisplayDelayMs</t>
   </si>
   <si>
     <r>
@@ -832,7 +891,7 @@
     </r>
   </si>
   <si>
-    <t>BattleInDurationMs</t>
+    <t>battleInDurationMs</t>
   </si>
   <si>
     <r>
@@ -845,7 +904,7 @@
     </r>
   </si>
   <si>
-    <t>BattleInScale</t>
+    <t>battleInScale</t>
   </si>
   <si>
     <r>
@@ -858,7 +917,7 @@
     </r>
   </si>
   <si>
-    <t>BattleInPunchScale</t>
+    <t>battleInPunchScale</t>
   </si>
   <si>
     <r>
@@ -887,7 +946,7 @@
     </r>
   </si>
   <si>
-    <t>BattleOutDurationMs</t>
+    <t>battleOutDurationMs</t>
   </si>
   <si>
     <r>
@@ -900,7 +959,7 @@
     </r>
   </si>
   <si>
-    <t>BattleActorCardOutPixels</t>
+    <t>battleActorCardOutPixels</t>
   </si>
   <si>
     <r>
@@ -916,7 +975,7 @@
     </r>
   </si>
   <si>
-    <t>BattleEnemyCardOutPixels</t>
+    <t>battleEnemyCardOutPixels</t>
   </si>
   <si>
     <r>
@@ -932,7 +991,7 @@
     </r>
   </si>
   <si>
-    <t>BattleInMoveIntervalMs</t>
+    <t>battleInMoveIntervalMs</t>
   </si>
   <si>
     <r>
@@ -942,6 +1001,32 @@
         <charset val="134"/>
       </rPr>
       <t>战斗入场卡片动画开始间隔</t>
+    </r>
+  </si>
+  <si>
+    <t>itemDragYOffset</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="微软雅黑"/>
+        <charset val="134"/>
+      </rPr>
+      <t>道具拖拽时相较于点击位置的偏移，像素</t>
+    </r>
+  </si>
+  <si>
+    <t>holdDistanceThreshold</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="微软雅黑"/>
+        <charset val="134"/>
+      </rPr>
+      <t>进入长按过程中回退到列表滚动的像素阈值</t>
     </r>
   </si>
 </sst>
@@ -1143,12 +1228,12 @@
     </font>
     <font>
       <sz val="12"/>
+      <color rgb="FF375623"/>
       <name val="微软雅黑"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="12"/>
-      <color rgb="FF375623"/>
       <name val="微软雅黑"/>
       <charset val="134"/>
     </font>
@@ -2138,7 +2223,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:F60"/>
+  <dimension ref="A1:F66"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="20" customHeight="1" outlineLevelCol="5"/>
   <cols>
     <col min="1" max="1" width="40.25" style="1" customWidth="1"/>
@@ -2332,20 +2417,20 @@
         <v>34</v>
       </c>
       <c r="E12" s="8" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="F12" s="7"/>
     </row>
     <row r="13" customHeight="1" spans="1:6">
       <c r="A13" s="7" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B13" s="7"/>
       <c r="C13" s="7" t="s">
         <v>6</v>
       </c>
       <c r="D13" s="7" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E13" s="8">
         <v>1000</v>
@@ -2354,14 +2439,14 @@
     </row>
     <row r="14" customHeight="1" spans="1:6">
       <c r="A14" s="7" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B14" s="7"/>
       <c r="C14" s="7" t="s">
         <v>6</v>
       </c>
       <c r="D14" s="7" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="E14" s="8">
         <v>2500</v>
@@ -2370,14 +2455,14 @@
     </row>
     <row r="15" customHeight="1" spans="1:6">
       <c r="A15" s="7" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B15" s="7"/>
       <c r="C15" s="7" t="s">
         <v>6</v>
       </c>
       <c r="D15" s="7" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="E15" s="8">
         <v>5000</v>
@@ -2386,17 +2471,17 @@
     </row>
     <row r="16" customHeight="1" spans="1:6">
       <c r="A16" s="7" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B16" s="7"/>
       <c r="C16" s="7" t="s">
         <v>15</v>
       </c>
       <c r="D16" s="7" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="E16" s="8" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F16" s="7"/>
     </row>
@@ -2410,7 +2495,7 @@
     </row>
     <row r="18" customHeight="1" spans="1:6">
       <c r="A18" s="5" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B18" s="5"/>
       <c r="C18" s="5"/>
@@ -2420,14 +2505,14 @@
     </row>
     <row r="19" customHeight="1" spans="1:6">
       <c r="A19" s="7" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B19" s="7"/>
       <c r="C19" s="7" t="s">
         <v>6</v>
       </c>
       <c r="D19" s="7" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="E19" s="8">
         <v>3000</v>
@@ -2436,14 +2521,14 @@
     </row>
     <row r="20" customHeight="1" spans="1:6">
       <c r="A20" s="7" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B20" s="7"/>
       <c r="C20" s="7" t="s">
         <v>6</v>
       </c>
       <c r="D20" s="7" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="E20" s="8">
         <v>1000</v>
@@ -2452,14 +2537,14 @@
     </row>
     <row r="21" customHeight="1" spans="1:6">
       <c r="A21" s="7" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B21" s="7"/>
       <c r="C21" s="7" t="s">
         <v>6</v>
       </c>
       <c r="D21" s="7" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E21" s="8">
         <v>4000</v>
@@ -2468,14 +2553,14 @@
     </row>
     <row r="22" customHeight="1" spans="1:6">
       <c r="A22" s="7" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B22" s="7"/>
       <c r="C22" s="7" t="s">
         <v>6</v>
       </c>
       <c r="D22" s="7" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="E22" s="8">
         <v>3000</v>
@@ -2484,14 +2569,14 @@
     </row>
     <row r="23" customHeight="1" spans="1:6">
       <c r="A23" s="7" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B23" s="7"/>
       <c r="C23" s="7" t="s">
         <v>6</v>
       </c>
       <c r="D23" s="7" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="E23" s="8">
         <v>4500</v>
@@ -2508,7 +2593,7 @@
     </row>
     <row r="25" customHeight="1" spans="1:6">
       <c r="A25" s="5" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B25" s="5"/>
       <c r="C25" s="5"/>
@@ -2518,14 +2603,14 @@
     </row>
     <row r="26" customHeight="1" spans="1:6">
       <c r="A26" s="7" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B26" s="7"/>
       <c r="C26" s="7" t="s">
         <v>6</v>
       </c>
       <c r="D26" s="7" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E26" s="8">
         <v>120</v>
@@ -2534,165 +2619,165 @@
     </row>
     <row r="27" customHeight="1" spans="1:6">
       <c r="A27" s="7" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B27" s="7"/>
       <c r="C27" s="7" t="s">
         <v>6</v>
       </c>
       <c r="D27" s="7" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E27" s="8">
-        <v>30</v>
+        <v>12</v>
       </c>
       <c r="F27" s="7"/>
     </row>
     <row r="28" customHeight="1" spans="1:6">
       <c r="A28" s="7" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B28" s="7"/>
       <c r="C28" s="7" t="s">
         <v>6</v>
       </c>
       <c r="D28" s="7" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E28" s="8">
-        <v>5</v>
+        <v>120</v>
       </c>
       <c r="F28" s="7"/>
     </row>
     <row r="29" customHeight="1" spans="1:6">
       <c r="A29" s="7" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="B29" s="7"/>
       <c r="C29" s="7" t="s">
         <v>6</v>
       </c>
       <c r="D29" s="7" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="E29" s="8">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F29" s="7"/>
     </row>
     <row r="30" customHeight="1" spans="1:6">
       <c r="A30" s="7" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B30" s="7"/>
       <c r="C30" s="7" t="s">
         <v>6</v>
       </c>
       <c r="D30" s="7" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="E30" s="8">
-        <v>4</v>
+        <v>30</v>
       </c>
       <c r="F30" s="7"/>
     </row>
     <row r="31" customHeight="1" spans="1:6">
       <c r="A31" s="7" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B31" s="7"/>
       <c r="C31" s="7" t="s">
         <v>6</v>
       </c>
       <c r="D31" s="7" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="E31" s="8">
+        <v>5</v>
+      </c>
+      <c r="F31" s="7"/>
+    </row>
+    <row r="32" customHeight="1" spans="1:6">
+      <c r="A32" s="7" t="s">
+        <v>69</v>
+      </c>
+      <c r="B32" s="7"/>
+      <c r="C32" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="D32" s="7" t="s">
+        <v>70</v>
+      </c>
+      <c r="E32" s="8">
+        <v>1</v>
+      </c>
+      <c r="F32" s="7"/>
+    </row>
+    <row r="33" customHeight="1" spans="1:6">
+      <c r="A33" s="7" t="s">
+        <v>71</v>
+      </c>
+      <c r="B33" s="7"/>
+      <c r="C33" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="D33" s="7" t="s">
+        <v>72</v>
+      </c>
+      <c r="E33" s="8">
         <v>4</v>
       </c>
-      <c r="F31" s="7"/>
-    </row>
-    <row r="32" customHeight="1" spans="1:6">
-      <c r="A32" s="7"/>
-      <c r="B32" s="7"/>
-      <c r="C32" s="7"/>
-      <c r="D32" s="7"/>
-      <c r="E32" s="8"/>
-      <c r="F32" s="7"/>
-    </row>
-    <row r="33" customHeight="1" spans="1:6">
-      <c r="A33" s="5" t="s">
-        <v>68</v>
-      </c>
-      <c r="B33" s="5"/>
-      <c r="C33" s="5"/>
-      <c r="D33" s="5"/>
-      <c r="E33" s="6"/>
-      <c r="F33" s="5"/>
+      <c r="F33" s="7"/>
     </row>
     <row r="34" customHeight="1" spans="1:6">
       <c r="A34" s="7" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="B34" s="7"/>
       <c r="C34" s="7" t="s">
         <v>6</v>
       </c>
       <c r="D34" s="7" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="E34" s="8">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F34" s="7"/>
     </row>
     <row r="35" customHeight="1" spans="1:6">
       <c r="A35" s="7" t="s">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="B35" s="7"/>
       <c r="C35" s="7" t="s">
         <v>6</v>
       </c>
       <c r="D35" s="7" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="E35" s="8">
-        <v>1</v>
+        <v>250</v>
       </c>
       <c r="F35" s="7"/>
     </row>
     <row r="36" customHeight="1" spans="1:6">
-      <c r="A36" s="7" t="s">
-        <v>73</v>
-      </c>
+      <c r="A36" s="7"/>
       <c r="B36" s="7"/>
-      <c r="C36" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="D36" s="7" t="s">
-        <v>74</v>
-      </c>
-      <c r="E36" s="8">
-        <v>500</v>
-      </c>
+      <c r="C36" s="7"/>
+      <c r="D36" s="7"/>
+      <c r="E36" s="8"/>
       <c r="F36" s="7"/>
     </row>
     <row r="37" customHeight="1" spans="1:6">
-      <c r="A37" s="7" t="s">
-        <v>75</v>
-      </c>
-      <c r="B37" s="7"/>
-      <c r="C37" s="7" t="s">
-        <v>76</v>
-      </c>
-      <c r="D37" s="7" t="s">
+      <c r="A37" s="5" t="s">
         <v>77</v>
       </c>
-      <c r="E37" s="8" t="b">
-        <v>0</v>
-      </c>
-      <c r="F37" s="7"/>
+      <c r="B37" s="5"/>
+      <c r="C37" s="5"/>
+      <c r="D37" s="5"/>
+      <c r="E37" s="6"/>
+      <c r="F37" s="5"/>
     </row>
     <row r="38" customHeight="1" spans="1:6">
       <c r="A38" s="7" t="s">
@@ -2700,12 +2785,12 @@
       </c>
       <c r="B38" s="7"/>
       <c r="C38" s="7" t="s">
-        <v>76</v>
+        <v>6</v>
       </c>
       <c r="D38" s="7" t="s">
         <v>79</v>
       </c>
-      <c r="E38" s="8" t="b">
+      <c r="E38" s="8">
         <v>1</v>
       </c>
       <c r="F38" s="7"/>
@@ -2716,13 +2801,13 @@
       </c>
       <c r="B39" s="7"/>
       <c r="C39" s="7" t="s">
-        <v>76</v>
+        <v>6</v>
       </c>
       <c r="D39" s="7" t="s">
         <v>81</v>
       </c>
-      <c r="E39" s="8" t="b">
-        <v>0</v>
+      <c r="E39" s="8">
+        <v>1</v>
       </c>
       <c r="F39" s="7"/>
     </row>
@@ -2732,13 +2817,13 @@
       </c>
       <c r="B40" s="7"/>
       <c r="C40" s="7" t="s">
-        <v>76</v>
+        <v>6</v>
       </c>
       <c r="D40" s="7" t="s">
         <v>83</v>
       </c>
-      <c r="E40" s="8" t="b">
-        <v>1</v>
+      <c r="E40" s="8">
+        <v>500</v>
       </c>
       <c r="F40" s="7"/>
     </row>
@@ -2748,232 +2833,324 @@
       </c>
       <c r="B41" s="7"/>
       <c r="C41" s="7" t="s">
-        <v>6</v>
+        <v>85</v>
       </c>
       <c r="D41" s="7" t="s">
-        <v>85</v>
-      </c>
-      <c r="E41" s="8">
-        <v>600</v>
+        <v>86</v>
+      </c>
+      <c r="E41" s="8" t="b">
+        <v>0</v>
       </c>
       <c r="F41" s="7"/>
     </row>
     <row r="42" customHeight="1" spans="1:6">
       <c r="A42" s="7" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="B42" s="7"/>
       <c r="C42" s="7" t="s">
-        <v>6</v>
+        <v>85</v>
       </c>
       <c r="D42" s="7" t="s">
-        <v>87</v>
-      </c>
-      <c r="E42" s="8">
-        <v>600</v>
+        <v>88</v>
+      </c>
+      <c r="E42" s="8" t="b">
+        <v>1</v>
       </c>
       <c r="F42" s="7"/>
     </row>
     <row r="43" customHeight="1" spans="1:6">
       <c r="A43" s="7" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B43" s="7"/>
       <c r="C43" s="7" t="s">
-        <v>6</v>
+        <v>85</v>
       </c>
       <c r="D43" s="7" t="s">
-        <v>89</v>
-      </c>
-      <c r="E43" s="8">
-        <v>600</v>
+        <v>90</v>
+      </c>
+      <c r="E43" s="8" t="b">
+        <v>0</v>
       </c>
       <c r="F43" s="7"/>
     </row>
     <row r="44" customHeight="1" spans="1:6">
       <c r="A44" s="7" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="B44" s="7"/>
       <c r="C44" s="7" t="s">
-        <v>6</v>
+        <v>85</v>
       </c>
       <c r="D44" s="7" t="s">
-        <v>91</v>
-      </c>
-      <c r="E44" s="8">
-        <v>32</v>
+        <v>92</v>
+      </c>
+      <c r="E44" s="8" t="b">
+        <v>1</v>
       </c>
       <c r="F44" s="7"/>
     </row>
     <row r="45" customHeight="1" spans="1:6">
-      <c r="A45" s="7"/>
+      <c r="A45" s="7" t="s">
+        <v>93</v>
+      </c>
       <c r="B45" s="7"/>
-      <c r="C45" s="7"/>
-      <c r="D45" s="7"/>
-      <c r="E45" s="8"/>
+      <c r="C45" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="D45" s="7" t="s">
+        <v>94</v>
+      </c>
+      <c r="E45" s="8">
+        <v>600</v>
+      </c>
       <c r="F45" s="7"/>
     </row>
     <row r="46" customHeight="1" spans="1:6">
-      <c r="A46" s="5" t="s">
-        <v>92</v>
-      </c>
-      <c r="B46" s="5"/>
-      <c r="C46" s="5"/>
-      <c r="D46" s="5"/>
-      <c r="E46" s="6"/>
-      <c r="F46" s="5"/>
+      <c r="A46" s="7" t="s">
+        <v>95</v>
+      </c>
+      <c r="B46" s="7"/>
+      <c r="C46" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="D46" s="7" t="s">
+        <v>96</v>
+      </c>
+      <c r="E46" s="8">
+        <v>600</v>
+      </c>
+      <c r="F46" s="7"/>
     </row>
     <row r="47" customHeight="1" spans="1:6">
       <c r="A47" s="7" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="B47" s="7"/>
       <c r="C47" s="7" t="s">
-        <v>94</v>
+        <v>6</v>
       </c>
       <c r="D47" s="7" t="s">
-        <v>95</v>
-      </c>
-      <c r="E47" s="8" t="s">
-        <v>96</v>
+        <v>98</v>
+      </c>
+      <c r="E47" s="8">
+        <v>600</v>
       </c>
       <c r="F47" s="7"/>
     </row>
+    <row r="48" customHeight="1" spans="1:6">
+      <c r="A48" s="7" t="s">
+        <v>99</v>
+      </c>
+      <c r="B48" s="7"/>
+      <c r="C48" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="D48" s="7" t="s">
+        <v>100</v>
+      </c>
+      <c r="E48" s="8">
+        <v>32</v>
+      </c>
+      <c r="F48" s="7"/>
+    </row>
+    <row r="49" customHeight="1" spans="1:6">
+      <c r="A49" s="7"/>
+      <c r="B49" s="7"/>
+      <c r="C49" s="7"/>
+      <c r="D49" s="7"/>
+      <c r="E49" s="8"/>
+      <c r="F49" s="7"/>
+    </row>
+    <row r="50" customHeight="1" spans="1:6">
+      <c r="A50" s="5" t="s">
+        <v>101</v>
+      </c>
+      <c r="B50" s="5"/>
+      <c r="C50" s="5"/>
+      <c r="D50" s="5"/>
+      <c r="E50" s="6"/>
+      <c r="F50" s="5"/>
+    </row>
     <row r="51" customHeight="1" spans="1:6">
-      <c r="A51" s="5" t="s">
-        <v>97</v>
-      </c>
-      <c r="B51" s="5"/>
-      <c r="C51" s="5"/>
-      <c r="D51" s="5"/>
-      <c r="E51" s="6"/>
-      <c r="F51" s="5"/>
-    </row>
-    <row r="52" customHeight="1" spans="1:6">
-      <c r="A52" s="1" t="s">
-        <v>98</v>
-      </c>
-      <c r="C52" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="D52" s="1" t="s">
-        <v>99</v>
-      </c>
-      <c r="E52" s="2">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="53" customHeight="1" spans="1:6">
-      <c r="A53" s="1" t="s">
-        <v>100</v>
-      </c>
-      <c r="C53" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="D53" s="1" t="s">
-        <v>101</v>
-      </c>
-      <c r="E53" s="2">
-        <v>1500</v>
-      </c>
-    </row>
-    <row r="54" customHeight="1" spans="1:6">
-      <c r="A54" s="1" t="s">
+      <c r="A51" s="7" t="s">
         <v>102</v>
       </c>
-      <c r="C54" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="D54" s="1" t="s">
+      <c r="B51" s="7"/>
+      <c r="C51" s="7" t="s">
         <v>103</v>
       </c>
-      <c r="E54" s="2">
-        <v>420</v>
-      </c>
+      <c r="D51" s="7" t="s">
+        <v>104</v>
+      </c>
+      <c r="E51" s="8" t="s">
+        <v>105</v>
+      </c>
+      <c r="F51" s="7"/>
     </row>
     <row r="55" customHeight="1" spans="1:6">
-      <c r="A55" s="1" t="s">
-        <v>104</v>
-      </c>
-      <c r="C55" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="D55" s="1" t="s">
-        <v>105</v>
-      </c>
-      <c r="E55" s="2">
-        <v>350</v>
-      </c>
+      <c r="A55" s="5" t="s">
+        <v>106</v>
+      </c>
+      <c r="B55" s="5"/>
+      <c r="C55" s="5"/>
+      <c r="D55" s="5"/>
+      <c r="E55" s="6"/>
+      <c r="F55" s="5"/>
     </row>
     <row r="56" customHeight="1" spans="1:6">
       <c r="A56" s="1" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C56" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D56" s="1" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="E56" s="2">
-        <v>120</v>
+        <v>250</v>
       </c>
     </row>
     <row r="57" customHeight="1" spans="1:6">
       <c r="A57" s="1" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C57" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D57" s="1" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="E57" s="2">
-        <v>350</v>
+        <v>1500</v>
       </c>
     </row>
     <row r="58" customHeight="1" spans="1:6">
       <c r="A58" s="1" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="C58" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D58" s="1" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="E58" s="2">
-        <v>15</v>
+        <v>420</v>
       </c>
     </row>
     <row r="59" customHeight="1" spans="1:6">
       <c r="A59" s="1" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="C59" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D59" s="1" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="E59" s="2">
-        <v>20</v>
+        <v>350</v>
       </c>
     </row>
     <row r="60" customHeight="1" spans="1:6">
       <c r="A60" s="1" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="C60" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D60" s="1" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="E60" s="2">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="61" customHeight="1" spans="1:6">
+      <c r="A61" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="C61" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D61" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="E61" s="2">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="62" customHeight="1" spans="1:6">
+      <c r="A62" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="C62" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D62" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="E62" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="63" customHeight="1" spans="1:6">
+      <c r="A63" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="C63" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D63" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="E63" s="2">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="64" customHeight="1" spans="1:6">
+      <c r="A64" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="C64" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D64" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="E64" s="2">
         <v>80</v>
+      </c>
+    </row>
+    <row r="65" customHeight="1" spans="1:5">
+      <c r="A65" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="C65" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D65" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="E65" s="2">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="66" customHeight="1" spans="1:5">
+      <c r="A66" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="C66" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D66" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="E66" s="2">
+        <v>15</v>
       </c>
     </row>
   </sheetData>
